--- a/nriss-patch-2/ig/ValueSet-fr-vs-actor-type-document.xlsx
+++ b/nriss-patch-2/ig/ValueSet-fr-vs-actor-type-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:58:47+00:00</t>
+    <t>2026-08-04T07:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-2/ig/ValueSet-fr-vs-actor-type-document.xlsx
+++ b/nriss-patch-2/ig/ValueSet-fr-vs-actor-type-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:44:41+00:00</t>
+    <t>2026-08-07T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
